--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_922_Iran_Persian_Gulf.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_922_Iran_Persian_Gulf.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Race25a23305d4fc7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R9645c8a026bf46cc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R7cd012df8d0142ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rc044573710794bb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Raa639216dc1e422e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R73f5faa3983d49e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Rbc03f07fe4a24af2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Red025362c30e405f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R756e0a74536c46d4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Ra92dd30f7abe44e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="Rbab20b8693734e28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R4b74d26caee444a7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ922CommercialTable" displayName="EEZ922CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ922CommercialTable" displayName="EEZ922CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ922FunctionalTable" displayName="EEZ922FunctionalTable" ref="A1:O23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O23"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ922FunctionalTable" displayName="EEZ922FunctionalTable" ref="A1:E23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E23"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ922ValidationTable" displayName="EEZ922ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ922ValidationTable" displayName="EEZ922ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -11749,7 +11703,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4895036cba26465f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6adaed05ae464d44"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -11759,20 +11713,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -11780,606 +11724,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>77.0436435597</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.34</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>218.77616239495518</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>77.0436435597</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$166,A2,'Species'!$U$2:$U$166))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>16855.31267491597</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.34</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>218.77616239495518</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>16855.31267491597</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>27794.051142750795</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.682249615961809</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>48.11157960699631</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>27794.051142750795</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>106.18604310413055</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$166,A3,'Species'!$U$2:$U$166))</x:f>
-        <x:v>2951340.312682545</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.682249615961809</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>48.11157960699631</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>1337215.7041553815</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>1614124.6085271633</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>2.2070787110196886</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>1.2070787110196886</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5671.5279802039</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.254425481723802</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>1796.492803098196</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5671.5279802039</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2201.768940655709</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$166,A4,'Species'!$U$2:$U$166))</x:f>
-        <x:v>12487394.152872754</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.254425481723802</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>1796.492803098196</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>10188859.199006354</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2298534.9538664</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2255929647247024</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2255929647247024</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>12114.160902840598</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.4652402205722534</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>291.9041171848226</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>12114.160902840598</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>727.7320886293899</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$166,A5,'Species'!$U$2:$U$166))</x:f>
-        <x:v>8815863.615816684</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.4652402205722534</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>291.9041171848226</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3536173.4437785787</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>5279690.172038106</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>2.4930518132041883</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>1.4930518132041886</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>128.2256915456</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.06</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>114.81536214968828</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>128.2256915456</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$166,A6,'Species'!$U$2:$U$166))</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>14722.279211702287</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.06</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>114.81536214968828</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
-        <x:v>14722.279211702287</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>157631.4406607495</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.3446012404222674</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>221.10636276325175</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>157631.4406607495</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>294.32370999533464</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$166,A7,'Species'!$U$2:$U$166))</x:f>
-        <x:v>46394670.42718124</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.3446012404222674</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>221.10636276325175</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>34853314.50162967</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>11541355.925551564</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.3311408424301199</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.3311408424301199</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>190277.8563091868</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.040059051247041</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1096.627294991248</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>190277.8563091868</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1795.166854062978</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$166,A8,'Species'!$U$2:$U$166))</x:f>
-        <x:v>341580500.70841026</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.040059051247041</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1096.627294991248</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>208663890.8610769</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>132916609.84733337</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.636989031973078</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.636989031973078</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>4235.0525155056</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.6553554425272594</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>452.22591122351935</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>4235.0525155056</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>466.3704248815047</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$166,A9,'Species'!$U$2:$U$166))</x:f>
-        <x:v>1975103.241051832</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.6553554425272594</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>452.22591122351935</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1915200.4829039779</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>59902.758147854125</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0312775391832738</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.03127753918327383</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>19522.4419120876</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.9274098739569125</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>846.0769702551763</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>19522.4419120876</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>1014.5506401417377</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$166,A10,'Species'!$U$2:$U$166))</x:f>
-        <x:v>19806505.939038366</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.9274098739569125</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>846.0769702551763</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>16517488.50496175</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3289017.4340766165</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.1991233372487964</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.1991233372487964</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>24231.533938805806</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.41670213759052</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>2610.370408510729</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>24231.533938805806</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2623.898614232997</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$166,A11,'Species'!$U$2:$U$166))</x:f>
-        <x:v>63581088.32277238</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.41670213759052</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>2610.370408510729</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>63253279.1466821</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>327809.1760902852</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0051824850903004</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.005182485090300336</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a3b0ac852234c0d"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdb8155b89da24df0"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -12389,20 +11939,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -12410,1254 +11950,440 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2906.8238106201998</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.6946896765021906</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>495.09629517636023</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2906.8238106201998</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>496.0215465899646</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$166,A2,'Species'!$U$2:$U$166))</x:f>
-        <x:v>1441847.2422083658</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.6946896765021906</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>495.09629517636023</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1439157.6993684906</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2689.542839875212</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0018688312205504</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.0018688312205503235</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>208.0580522063</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.382564374522967</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>241.3039185614621</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>208.0580522063</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>267.6907035954358</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$166,A3,'Species'!$U$2:$U$166))</x:f>
-        <x:v>55695.20638380037</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.382564374522967</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>241.3039185614621</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>50205.22328564544</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>5489.983098154924</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.109350835209304</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.10935083520930394</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>36361.4193163657</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.317856482181187</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2079.0095399417733</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>36361.4193163657</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2518.310354091204</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$166,A4,'Species'!$U$2:$U$166))</x:f>
-        <x:v>91569338.75385563</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.317856482181187</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2079.0095399417733</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>75595737.64454736</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>15973601.109308273</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2113029333005052</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2113029333005051</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>7269.862711912199</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.662871772205433</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>460.1207003984439</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>7269.862711912199</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>559.5545619517549</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$166,A5,'Species'!$U$2:$U$166))</x:f>
-        <x:v>4067884.845213427</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.662871772205433</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>460.1207003984439</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>3345014.322805572</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>722870.5224078554</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.2161038646320534</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.2161038646320535</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>56784.5709556274</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.410438131984538</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2572.990199472762</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>56784.5709556274</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2697.2294958331695</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$166,A6,'Species'!$U$2:$U$166))</x:f>
-        <x:v>153161019.68974975</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.410438131984538</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2572.990199472762</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>146106144.55009496</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>7054875.139654785</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.048285957865625</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.048285957865624896</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>6459.7092771489</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.6335282876612083</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>430.0592445183861</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>6459.7092771489</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>554.3453902931511</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$166,A7,'Species'!$U$2:$U$166))</x:f>
-        <x:v>3580910.0604213956</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.6335282876612083</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>430.0592445183861</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>2778057.691539066</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>802852.3688823297</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.2889977307985794</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.2889977307985793</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>43366.008297534296</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.293647174878253</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1966.2882087066587</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>43366.008297534296</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2297.633922741716</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$166,A8,'Species'!$U$2:$U$166))</x:f>
-        <x:v>99639211.75831354</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.293647174878253</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1966.2882087066587</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>85270070.77411681</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>14369140.984196723</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1685132996108452</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.1685132996108452</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>11423.747638995199</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.093574846132984</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1240.4373831690039</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>11423.747638995199</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1293.2712823842396</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$166,A9,'Species'!$U$2:$U$166))</x:f>
-        <x:v>14774004.75871725</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.093574846132984</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1240.4373831690039</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>14170443.62729829</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>603561.1314189602</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0425929594932544</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.04259295949325434</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>11609.4452743245</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.742679357388233</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>55.29417177907295</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>11609.4452743245</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>110.68162226353195</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$166,A10,'Species'!$U$2:$U$166))</x:f>
-        <x:v>1284952.2365419304</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.742679357388233</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>55.29417177907295</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>641934.6612582456</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>643017.5752836848</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>2.001686953658674</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>1.0016869536586739</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>19729.5554270624</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.230181298160295</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>169.8952739812379</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>19729.5554270624</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>218.36407209770726</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$166,A11,'Species'!$U$2:$U$166))</x:f>
-        <x:v>4308226.063730766</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.230181298160295</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>169.8952739812379</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>3351958.2248087856</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>956267.8389219805</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.285286323631474</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.28528632363147405</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>145841.58476047483</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.369570604560135</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>234.19121759287572</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>145841.58476047483</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>309.33689223202344</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$166,A12,'Species'!$U$2:$U$166))</x:f>
-        <x:v>45114182.58799852</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.369570604560135</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>234.19121759287572</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>34154818.31073019</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>10959364.277268328</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3208731540470615</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.32087315404706157</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>25517.002052145705</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.8581895013148646</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>721.4221979711936</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>25517.002052145705</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>1300.1038578436262</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$166,A13,'Species'!$U$2:$U$166))</x:f>
-        <x:v>33174752.808598354</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.8581895013148646</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>721.4221979711936</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>18408531.70609441</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>14766221.102503944</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.8021400803854102</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.8021400803854103</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>26695.3767351345</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.435242151527486</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>272.4219840199479</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>26695.3767351345</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>691.8490806192785</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$166,A14,'Species'!$U$2:$U$166))</x:f>
-        <x:v>18469171.850988083</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.435242151527486</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>272.4219840199479</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>7272407.4943453</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>11196764.356642783</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.539622795525263</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.5396227955252628</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>264.6944669387</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.7764359824582683</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>59.76349433163223</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>264.6944669387</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>72.30344646664118</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$166,A15,'Species'!$U$2:$U$166))</x:f>
-        <x:v>19138.322220318416</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.7764359824582683</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>59.76349433163223</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>15819.06627450541</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>3319.2559458130054</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.2098262873556855</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.20982628735568548</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>16184.605868426299</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>2.6389025130582855</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>43.5414124444905</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>16184.605868426299</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>102.961300984875</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$166,A16,'Species'!$U$2:$U$166))</x:f>
-        <x:v>1666388.0761406142</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>2.6389025130582855</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>43.5414124444905</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>704700.5993686707</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>961687.4767719435</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>2.3646752644080378</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>1.364675264408038</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>312.33653917159995</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.1468374327516986</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>140.22886946989175</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>312.33653917159995</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>145.63843667747307</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$166,A17,'Species'!$U$2:$U$166))</x:f>
-        <x:v>45488.205282204144</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.1468374327516986</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>140.22886946989175</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>43798.59978217202</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>1689.6055000321212</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0385767012743605</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.038576701274360505</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>8670.4944869192</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.6750388892369976</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>473.1936295558122</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>8670.4944869192</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>545.9239991661952</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$166,A18,'Species'!$U$2:$U$166))</x:f>
-        <x:v>4733431.025047378</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.6750388892369976</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>473.1936295558122</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>4102822.756308956</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>630608.2687384216</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.153701075136314</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.15370107513631395</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>9977.522075155599</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.131689852242412</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>135.42219607012478</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>9977.522075155599</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>161.05973385809455</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$166,A19,'Species'!$U$2:$U$166))</x:f>
-        <x:v>1606977.049987824</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.131689852242412</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>135.42219607012478</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1351177.9507557198</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>255799.09923210414</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.1893156257390336</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.18931562573903354</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>4790.003974925</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>4.013539360322041</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>1031.6665756507239</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>4790.003974925</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>1038.0865075627107</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$166,A20,'Species'!$U$2:$U$166))</x:f>
-        <x:v>4972438.497541395</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>4.013539360322041</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>1031.6665756507239</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>4941686.998164231</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>30751.49937716406</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.006222874777093</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.006222874777092887</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>5671.5279802039</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>4.254425481723802</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>1796.492803098196</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>5671.5279802039</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>2201.768940655709</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$166,A21,'Species'!$U$2:$U$166))</x:f>
-        <x:v>12487394.152872754</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>4.254425481723802</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>1796.492803098196</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>10188859.199006354</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>2298534.9538664</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.2255929647247024</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.2255929647247024</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>551.1329792</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.76</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>575.4399373371566</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>551.1329792</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>575.4399373371566</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$166,A22,'Species'!$U$2:$U$166))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>317143.92701528844</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.76</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>575.4399373371566</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>317143.92701528844</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>1087.8520167435</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>4.012373639208341</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>1028.901118196353</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>1087.8520167435</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>1042.8322744488803</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$166,A23,'Species'!$U$2:$U$166))</x:f>
-        <x:v>1134447.1928844254</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>4.012373639208341</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>1028.901118196353</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>1119292.1564595448</x:v>
       </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>15155.036424880615</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0135398397437339</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.013539839743733942</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G23">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O23">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb53403ec01f74d91"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbf5ae0de747d4a70"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13832,7 +12558,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -13931,7 +12657,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>497624044.3117129</x:v>
+        <x:v>340296999.4360813</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13945,7 +12671,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>497624044.311713</x:v>
+        <x:v>415369783.1834287</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13959,7 +12685,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-157327044.87563163</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13973,7 +12699,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>5.960464477539063e-8</x:v>
+        <x:v>-82254261.12828422</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -13984,9 +12710,9 @@
         <x:v>EEZ_922</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -13998,47 +12724,19 @@
         <x:v>EEZ_922</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_922</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_922</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R199919bc55604242"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3fdcb44d0eaa467a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14085,7 +12783,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
